--- a/data/trans_dic/P16A03-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A03-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,22</t>
+          <t>2,01; 4,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,97</t>
+          <t>0,87; 2,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,58</t>
+          <t>0,86; 2,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,22</t>
+          <t>2,96; 6,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,34; 8,18</t>
+          <t>5,48; 8,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,61; 9,72</t>
+          <t>6,65; 9,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,96; 7,05</t>
+          <t>4,03; 7,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,76; 9,97</t>
+          <t>6,87; 9,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,26; 6,13</t>
+          <t>4,23; 6,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 6,46</t>
+          <t>4,62; 6,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 4,75</t>
+          <t>2,81; 4,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,57; 7,77</t>
+          <t>5,65; 7,92</t>
         </is>
       </c>
     </row>
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,04</t>
+          <t>0,89; 2,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,64</t>
+          <t>0,69; 1,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,71</t>
+          <t>0,74; 1,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,42 +877,42 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,61; 5,79</t>
+          <t>3,61; 5,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,43; 5,55</t>
+          <t>3,45; 5,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 4,25</t>
+          <t>2,57; 4,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,75; 4,78</t>
+          <t>2,73; 4,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 3,57</t>
+          <t>2,44; 3,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,26</t>
+          <t>2,14; 3,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,73</t>
+          <t>1,81; 2,77</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,15</t>
+          <t>2,06; 3,16</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,55</t>
+          <t>1,95; 5,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,66</t>
+          <t>0,58; 3,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,35</t>
+          <t>0,41; 2,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,15</t>
+          <t>0,96; 3,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,68</t>
+          <t>1,97; 5,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,67; 8,45</t>
+          <t>3,8; 8,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,75</t>
+          <t>3,16; 6,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 6,57</t>
+          <t>3,46; 6,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,72</t>
+          <t>2,28; 4,71</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,19</t>
+          <t>2,44; 4,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,14</t>
+          <t>2,02; 4,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,44</t>
+          <t>2,51; 4,4</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,9</t>
+          <t>1,75; 2,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 1,85</t>
+          <t>0,94; 1,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,7</t>
+          <t>0,93; 1,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,54</t>
+          <t>1,47; 2,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 6,06</t>
+          <t>4,58; 6,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,2; 6,78</t>
+          <t>5,23; 6,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 4,9</t>
+          <t>3,5; 4,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 5,55</t>
+          <t>4,03; 5,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,31; 4,24</t>
+          <t>3,35; 4,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,24; 4,2</t>
+          <t>3,23; 4,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 3,16</t>
+          <t>2,34; 3,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,02; 3,99</t>
+          <t>2,99; 3,95</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20424; 43490</t>
+          <t>20695; 44612</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8613; 28827</t>
+          <t>8469; 27461</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6803; 19482</t>
+          <t>6505; 19939</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15384; 31946</t>
+          <t>15175; 31779</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>70220; 107611</t>
+          <t>72076; 108029</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88066; 129555</t>
+          <t>88595; 130431</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39363; 70081</t>
+          <t>40056; 69957</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50815; 74947</t>
+          <t>51608; 74012</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>99860; 143821</t>
+          <t>99330; 141150</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>105048; 148916</t>
+          <t>106415; 148763</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51052; 82999</t>
+          <t>49168; 83236</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>70456; 98299</t>
+          <t>71465; 100206</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15569; 34540</t>
+          <t>15079; 36030</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12684; 32058</t>
+          <t>13462; 32716</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15236; 35452</t>
+          <t>15445; 35053</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22478; 47875</t>
+          <t>22504; 47830</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57330; 91925</t>
+          <t>57295; 91534</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60019; 97077</t>
+          <t>60370; 95575</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51872; 84555</t>
+          <t>51102; 82458</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>61456; 107007</t>
+          <t>61113; 105231</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>78562; 117231</t>
+          <t>80125; 118337</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>80412; 120979</t>
+          <t>79346; 120073</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70894; 110940</t>
+          <t>73553; 112586</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>93525; 142713</t>
+          <t>93418; 142952</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11223; 30576</t>
+          <t>10752; 28922</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3009; 17602</t>
+          <t>2767; 16640</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2154; 12860</t>
+          <t>2225; 12792</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6176; 20354</t>
+          <t>6239; 21070</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10394; 27065</t>
+          <t>9376; 26255</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16788; 38654</t>
+          <t>17404; 37067</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17499; 37062</t>
+          <t>17342; 37523</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23515; 43397</t>
+          <t>22838; 43053</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25334; 48547</t>
+          <t>23417; 48362</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22734; 48726</t>
+          <t>22878; 46671</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22617; 45394</t>
+          <t>22160; 44635</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32576; 58085</t>
+          <t>32814; 57518</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>58615; 94985</t>
+          <t>57390; 91669</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32017; 62967</t>
+          <t>32220; 61974</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31450; 57255</t>
+          <t>31466; 57091</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50955; 87609</t>
+          <t>50859; 85680</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>154147; 204663</t>
+          <t>154672; 206254</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>183913; 239912</t>
+          <t>185191; 242673</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>124896; 173078</t>
+          <t>123773; 172110</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>147543; 202463</t>
+          <t>146893; 208149</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>220429; 281987</t>
+          <t>222735; 286084</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>225138; 291876</t>
+          <t>224630; 291014</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>163180; 218496</t>
+          <t>161569; 215108</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>214440; 283157</t>
+          <t>212256; 280387</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A03-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A03-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,32</t>
+          <t>1,92; 4,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,83</t>
+          <t>0,98; 3,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,64</t>
+          <t>0,82; 2,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 6,19</t>
+          <t>2,55; 5,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 8,21</t>
+          <t>5,59; 8,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,65; 9,79</t>
+          <t>6,65; 9,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,03; 7,03</t>
+          <t>3,9; 6,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,87; 9,85</t>
+          <t>6,78; 9,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 6,01</t>
+          <t>4,17; 6,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,46</t>
+          <t>4,5; 6,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,76</t>
+          <t>2,91; 4,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,65; 7,92</t>
+          <t>5,31; 7,49</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,13</t>
+          <t>0,92; 2,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,67</t>
+          <t>0,65; 1,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,69</t>
+          <t>0,72; 1,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,09</t>
+          <t>1,29; 2,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,61; 5,77</t>
+          <t>3,65; 5,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 5,46</t>
+          <t>3,49; 5,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,15</t>
+          <t>2,65; 4,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,7</t>
+          <t>3,76; 5,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 3,61</t>
+          <t>2,41; 3,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,24</t>
+          <t>2,12; 3,22</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 2,77</t>
+          <t>1,78; 2,71</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,16</t>
+          <t>2,73; 3,67</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,25</t>
+          <t>2,01; 5,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,46</t>
+          <t>0,61; 3,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,34</t>
+          <t>0,42; 2,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,26</t>
+          <t>0,88; 2,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,51</t>
+          <t>2,21; 5,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 8,1</t>
+          <t>3,78; 8,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,16; 6,83</t>
+          <t>3,11; 6,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 6,52</t>
+          <t>3,74; 6,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,71</t>
+          <t>2,44; 4,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,98</t>
+          <t>2,58; 5,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,07</t>
+          <t>1,99; 4,14</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 4,4</t>
+          <t>2,52; 4,26</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,8</t>
+          <t>1,74; 2,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 1,82</t>
+          <t>0,93; 1,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,69</t>
+          <t>0,89; 1,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,48</t>
+          <t>1,75; 2,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,58; 6,1</t>
+          <t>4,52; 6,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 6,86</t>
+          <t>5,16; 6,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,5; 4,87</t>
+          <t>3,53; 4,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 5,7</t>
+          <t>4,71; 5,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,35; 4,3</t>
+          <t>3,37; 4,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 4,19</t>
+          <t>3,3; 4,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,11</t>
+          <t>2,34; 3,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 3,95</t>
+          <t>3,41; 4,21</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22337</t>
+          <t>22708</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>62511</t>
+          <t>65462</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84848</t>
+          <t>88170</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20695; 44612</t>
+          <t>19784; 43819</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8469; 27461</t>
+          <t>9553; 30129</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6505; 19939</t>
+          <t>6197; 19805</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15175; 31779</t>
+          <t>14695; 31718</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>72076; 108029</t>
+          <t>73536; 108201</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88595; 130431</t>
+          <t>88569; 131691</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40056; 69957</t>
+          <t>38773; 69369</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>51608; 74012</t>
+          <t>55569; 79401</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>99330; 141150</t>
+          <t>97784; 141671</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>106415; 148763</t>
+          <t>103664; 146628</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49168; 83236</t>
+          <t>50924; 86684</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>71465; 100206</t>
+          <t>74205; 104612</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34305</t>
+          <t>41314</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>85205</t>
+          <t>96679</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>119510</t>
+          <t>137993</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15079; 36030</t>
+          <t>15555; 34624</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13462; 32716</t>
+          <t>12736; 33291</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15445; 35053</t>
+          <t>14933; 35274</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22504; 47830</t>
+          <t>28676; 56773</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57295; 91534</t>
+          <t>57983; 89655</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60370; 95575</t>
+          <t>61069; 97976</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51102; 82458</t>
+          <t>52777; 85480</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>61113; 105231</t>
+          <t>81562; 115018</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>80125; 118337</t>
+          <t>79202; 119976</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>79346; 120073</t>
+          <t>78804; 119358</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73553; 112586</t>
+          <t>72445; 110231</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>93418; 142952</t>
+          <t>120048; 161436</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12072</t>
+          <t>12161</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31595</t>
+          <t>35982</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>43667</t>
+          <t>48143</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10752; 28922</t>
+          <t>11061; 29962</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2767; 16640</t>
+          <t>2907; 17724</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2225; 12792</t>
+          <t>2278; 13960</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6239; 21070</t>
+          <t>6284; 21126</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9376; 26255</t>
+          <t>10507; 26702</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17404; 37067</t>
+          <t>17318; 38555</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17342; 37523</t>
+          <t>17082; 37230</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22838; 43053</t>
+          <t>27508; 47774</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23417; 48362</t>
+          <t>25055; 49083</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22878; 46671</t>
+          <t>24221; 48723</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22160; 44635</t>
+          <t>21794; 45348</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32814; 57518</t>
+          <t>36463; 61663</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68715</t>
+          <t>76183</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>179311</t>
+          <t>198124</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>248026</t>
+          <t>274307</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>57390; 91669</t>
+          <t>56909; 93723</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32220; 61974</t>
+          <t>31848; 61503</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31466; 57091</t>
+          <t>30169; 57794</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50859; 85680</t>
+          <t>61675; 96733</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>154672; 206254</t>
+          <t>152853; 207030</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>185191; 242673</t>
+          <t>182794; 244535</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>123773; 172110</t>
+          <t>124807; 171575</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>146893; 208149</t>
+          <t>175594; 222999</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>222735; 286084</t>
+          <t>224272; 290756</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>224630; 291014</t>
+          <t>229351; 293620</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>161569; 215108</t>
+          <t>161701; 213706</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>212256; 280387</t>
+          <t>247095; 304685</t>
         </is>
       </c>
     </row>
